--- a/output/pdf_financials_xlsx/BLCO.xlsx
+++ b/output/pdf_financials_xlsx/BLCO.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-43</v>
+        <v>-49</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-330</v>
+        <v>-345</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-376</v>
+        <v>-391</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-387</v>
+        <v>-399</v>
       </c>
     </row>
     <row r="28">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-43</v>
+        <v>-49</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-330</v>
+        <v>-345</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-376</v>
+        <v>-391</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-387</v>
+        <v>-399</v>
       </c>
     </row>
     <row r="30">
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1.141188959660297</v>
+        <v>-1.300424628450106</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-7.959479015918958</v>
+        <v>-8.321273516642547</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-7.848048424128574</v>
+        <v>-8.161135462325193</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-7.586747696530092</v>
+        <v>-7.821995687120173</v>
       </c>
     </row>
     <row r="31">
@@ -1963,7 +1963,7 @@
         <v>1309</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1493</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="76">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLCO.xlsx
+++ b/output/pdf_financials_xlsx/BLCO.xlsx
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-49</v>
+        <v>195</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-345</v>
+        <v>-105</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-391</v>
+        <v>-103</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-399</v>
+        <v>-141</v>
       </c>
     </row>
     <row r="30">
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1.300424628450106</v>
+        <v>5.17515923566879</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-8.321273516642547</v>
+        <v>-2.532561505065123</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-8.161135462325193</v>
+        <v>-2.149864328950115</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-7.821995687120173</v>
+        <v>-2.764163889433444</v>
       </c>
     </row>
     <row r="31">
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
     </row>
     <row r="101">
@@ -4356,7 +4356,11 @@
           <t>Depreciation and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>379</v>
       </c>
@@ -6074,7 +6078,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLCO.xlsx
+++ b/output/pdf_financials_xlsx/BLCO.xlsx
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>3020</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>3169</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="57">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>1630</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="58">
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-147</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104">
@@ -2577,16 +2577,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-106</v>
+        <v>-113</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-264</v>
+        <v>-411</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-147</v>
+        <v>14</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107">
@@ -2729,16 +2729,16 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="115">
@@ -2748,16 +2748,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116">
@@ -4842,7 +4842,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>-7</v>
       </c>
@@ -5000,7 +5004,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>-17</v>
       </c>
@@ -5030,7 +5038,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>22</v>
       </c>
